--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:AB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,45 +484,75 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>SOXX</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>52週高</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>距高%</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>VIX</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>總 YoY%</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>核心 YoY%</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>10Y%</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>月變動%</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>10Y-2Y 利差%</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>註</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>MOVE</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>衰退機率%</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>去年同期%</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>當季加總(億美)</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>計入家數</t>
         </is>
@@ -569,6 +599,12 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -586,11 +622,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4040.2</v>
+        <v>4039.6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>FMP=4040.2</t>
+          <t>FMP=4039.6</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -609,6 +645,12 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -628,12 +670,12 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FRED=78.94, FMP=91.73</t>
+          <t>FRED=78.94</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>85.34</v>
+        <v>78.94</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -651,6 +693,12 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -670,14 +718,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FRED=0.7019, FMP=0.6887</t>
+          <t>FRED=0.7019, FMP=0.6889</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.6953</v>
+        <v>0.6954</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -689,6 +737,12 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -721,6 +775,12 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -732,27 +792,39 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>🟢 健康</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>❌ 無資料</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>612.61</v>
+      </c>
+      <c r="O7" t="n">
+        <v>655.95</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-6.6</v>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -772,7 +844,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FRED=18.41, FMP=17.84</t>
+          <t>FRED=18.41, FMP=17.77</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -780,17 +852,23 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>18.12</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>18.09</v>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -819,18 +897,24 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
         <v>4.27</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>2.96</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -857,16 +941,22 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="n">
         <v>4.4</v>
       </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
         <v>-0.1</v>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -878,18 +968,18 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>🟡 平坦</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>⚠️ 需要 FMP 期貨權限,改用 CME 官網查</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -898,7 +988,19 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fed Futures 抓不到,用利差代理</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -910,18 +1012,18 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>🟢 平靜(&lt;100)</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>⚠️ FMP 可能不支援 ^MOVE,改抓 ICE 官網</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -931,6 +1033,14 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -963,12 +1073,18 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -989,7 +1105,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌ 無資料</t>
+          <t>❌ 無資料(FRED OECD series 變動)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1001,6 +1117,12 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1021,7 +1143,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌ 無資料(可改抓主計總處)</t>
+          <t>❌ 無資料(可改抓主計總處 stat.gov.tw)</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1033,6 +1155,12 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1065,10 +1193,16 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="n">
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="n">
         <v>1297.5</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AB16" t="n">
         <v>4</v>
       </c>
     </row>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>MOVE</t>
+          <t>TLT 30日年化波動%</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4039.6</v>
+        <v>4031.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>FMP=4039.6</t>
+          <t>FMP=4031.8</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -718,7 +718,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FRED=0.7019, FMP=0.6889</t>
+          <t>FRED=0.7019, FMP=0.6890</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -763,7 +763,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>❌ 無資料(可手動查財政部)</t>
+          <t>❌ FRED+OECD 都失敗,手動查 https://web02.mof.gov.tw/njswww/WebMain.aspx</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -805,13 +805,13 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>612.61</v>
+        <v>610.11</v>
       </c>
       <c r="O7" t="n">
         <v>655.95</v>
       </c>
       <c r="P7" t="n">
-        <v>-6.6</v>
+        <v>-7</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -844,7 +844,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FRED=18.41, FMP=17.77</t>
+          <t>FRED=18.41, FMP=17.60</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -856,7 +856,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>18.09</v>
+        <v>18.01</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢 平靜(&lt;100)</t>
+          <t>🟢 平靜(&lt;10%)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1033,9 +1033,13 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>MOVE 代理</t>
+        </is>
+      </c>
       <c r="X12" t="n">
-        <v>21.02</v>
+        <v>8.5</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4031.8</v>
+        <v>4028.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>FMP=4031.8</t>
+          <t>FMP=4028.7</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -718,14 +718,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FRED=0.7019, FMP=0.6890</t>
+          <t>FRED=0.6907, FMP=0.6921</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.6954</v>
+        <v>0.6914</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -794,7 +794,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟢 健康</t>
+          <t>🔴 新高過熱</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -805,13 +805,13 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>610.11</v>
+        <v>640.76</v>
       </c>
       <c r="O7" t="n">
         <v>655.95</v>
       </c>
       <c r="P7" t="n">
-        <v>-7</v>
+        <v>-2.3</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -844,7 +844,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FRED=18.41, FMP=17.60</t>
+          <t>FRED=17.65, FMP=16.45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -856,7 +856,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>18.01</v>
+        <v>17.05</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
@@ -945,10 +945,10 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -989,7 +989,7 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="X12" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -565,17 +565,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>331.3</v>
+        <v>330.9</v>
       </c>
       <c r="C2" t="n">
-        <v>329.1</v>
+        <v>328.1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.66</v>
+        <v>0.84</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4028.7</v>
+        <v>4187.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>FMP=4028.7</t>
+          <t>FMP=4187.3</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -670,16 +670,16 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FRED=78.94</t>
+          <t>FRED=71.87</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>78.94</v>
+        <v>71.87</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>412134</t>
+          <t>408359</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -718,14 +718,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FRED=0.6907, FMP=0.6921</t>
+          <t>FRED=0.6907, FMP=0.6943</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.6914</v>
+        <v>0.6925</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -794,7 +794,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🔴 新高過熱</t>
+          <t>🟢 健康</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -805,13 +805,13 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>640.76</v>
+        <v>566.3200000000001</v>
       </c>
       <c r="O7" t="n">
         <v>655.95</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3</v>
+        <v>-13.7</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -844,7 +844,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FRED=17.65, FMP=16.45</t>
+          <t>FRED=16.59, FMP=15.81</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -856,7 +856,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>17.05</v>
+        <v>16.2</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
@@ -945,10 +945,10 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>4.38</v>
+        <v>4.48</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -989,7 +989,7 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="X12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1084,9 +1084,11 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
     </row>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,112 +449,72 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>價格</t>
+          <t>狀態</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>WTI</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>資料源</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>誤差</t>
-        </is>
-      </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>WTI</t>
+          <t>Cushing 庫存(千桶)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Cushing 庫存(千桶)</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>狀態</t>
+          <t>總 YoY%</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>核心 YoY%</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>52週高</t>
+          <t>10Y%</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>距高%</t>
+          <t>月變動%</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>10Y-2Y 利差%</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>總 YoY%</t>
+          <t>註</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>核心 YoY%</t>
+          <t>衰退機率%</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>10Y%</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>月變動%</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>10Y-2Y 利差%</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>註</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>TLT 30日年化波動%</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>衰退機率%</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
           <t>去年同期%</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>當季加總(億美)</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>計入家數</t>
         </is>
       </c>
     </row>
@@ -597,14 +557,6 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -616,22 +568,14 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>🟢 強(央行買盤)</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>4187.3</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>FMP=4187.3</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>❌ 無資料</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -643,14 +587,6 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -668,20 +604,20 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>FRED=71.87</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>71.87</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>408359</t>
-        </is>
-      </c>
+      <c r="H4" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FRED=69.60</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>411357</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -691,14 +627,6 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -716,17 +644,17 @@
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>FRED=0.6907, FMP=0.6943</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>FRED=0.6931</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0.6925</v>
-      </c>
+      <c r="K5" t="n">
+        <v>0.6931</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -735,14 +663,6 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -755,17 +675,17 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>❌ FRED+OECD 都失敗,手動查 https://web02.mof.gov.tw/njswww/WebMain.aspx</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>❌ FRED+OECD 都失敗,手動查 https://web02.mof.gov.tw/njswww/WebMain.aspx</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -773,14 +693,6 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -792,39 +704,25 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>🟢 健康</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>❌ 無資料</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>566.3200000000001</v>
-      </c>
-      <c r="O7" t="n">
-        <v>655.95</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-13.7</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -842,33 +740,25 @@
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>FRED=16.59, FMP=15.81</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FRED=15.84</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>15.84</v>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -895,26 +785,18 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.96</v>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.96</v>
-      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -928,7 +810,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟡 中性(3.5-4.5)</t>
+          <t>🔴 緊縮股不利(&gt;4.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -939,24 +821,16 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -983,24 +857,16 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Fed Futures 抓不到,用利差代理</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Fed Futures 抓不到,用利差代理</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1012,12 +878,12 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>🟢 平靜(&lt;10%)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>❌ MOVE 與 TLT 都抓不到</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1031,20 +897,6 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>MOVE 代理</t>
-        </is>
-      </c>
-      <c r="X12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1077,20 +929,10 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1103,17 +945,17 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>❌ 無資料(FRED OECD series 變動)</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>❌ 無資料(FRED OECD series 變動)</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -1121,14 +963,6 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1141,17 +975,17 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>❌ 無資料(可改抓主計總處 stat.gov.tw)</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>❌ 無資料(可改抓主計總處 stat.gov.tw)</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -1159,14 +993,6 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1176,16 +1002,14 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
-        <v>80.5</v>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>🟢🟢 AI 需求爆(&gt;50%)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>❌ 無資料</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1199,18 +1023,6 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="n">
-        <v>1297.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>4</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -605,16 +605,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>69.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=69.60</t>
+          <t>FRED=79.20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>411357</t>
+          <t>409665</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.6931</t>
+          <t>FRED=0.6959</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.6931</v>
+        <v>0.6959</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=15.84</t>
+          <t>FRED=16.73</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>15.84</v>
+        <v>16.73</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -771,7 +771,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -786,10 +786,10 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>4.27</v>
+        <v>3.73</v>
       </c>
       <c r="N9" t="n">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -822,10 +822,10 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>4.54</v>
+        <v>4.57</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.02</v>
+        <v>0.1</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,72 +449,92 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>價格</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>資料源</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>誤差</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>WTI</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Cushing 庫存(千桶)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>AUDUSD</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>狀態</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>WTI</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>資料源</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Cushing 庫存(千桶)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>AUDUSD</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>VIX</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>總 YoY%</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>核心 YoY%</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>10Y%</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>月變動%</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>10Y-2Y 利差%</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>註</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>衰退機率%</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>去年同期%</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>當季加總(億美)</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>計入家數</t>
         </is>
       </c>
     </row>
@@ -557,6 +577,10 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -568,14 +592,22 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>❌ 無資料</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🟢 強(央行買盤)</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>4070.8</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>FMP=4070.8</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -587,6 +619,10 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -604,20 +640,20 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>FRED=79.20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>409665</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FRED=84.38</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>84.38</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>411675</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -627,6 +663,10 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -644,17 +684,17 @@
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>FRED=0.6959</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FRED=0.6985, FMP=0.6984</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>0.6959</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0.6984</v>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -663,6 +703,10 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -675,17 +719,17 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>❌ FRED+OECD 都失敗,手動查 https://web02.mof.gov.tw/njswww/WebMain.aspx</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>❌ FRED+OECD 都失敗,手動查 https://web02.mof.gov.tw/njswww/WebMain.aspx</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -693,6 +737,10 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -705,17 +753,17 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>❌ 無資料</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>❌ 無資料</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -723,6 +771,10 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -740,25 +792,29 @@
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>FRED=16.73</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>FRED=18.70, FMP=18.58</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>16.73</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>18.64</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -785,18 +841,22 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>3.73</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>2.81</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -821,16 +881,20 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.21</v>
+      </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -857,16 +921,20 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>Fed Futures 抓不到,用利差代理</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -879,17 +947,17 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>❌ MOVE 與 TLT 都抓不到</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>❌ MOVE 與 TLT 都抓不到</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -897,6 +965,10 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -929,10 +1001,14 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="n">
         <v>0.5</v>
       </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -945,17 +1021,17 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>❌ 無資料(FRED OECD series 變動)</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>❌ 無資料(FRED OECD series 變動)</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -963,6 +1039,10 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -975,17 +1055,17 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>❌ 無資料(可改抓主計總處 stat.gov.tw)</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>❌ 無資料(可改抓主計總處 stat.gov.tw)</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -993,6 +1073,10 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1002,14 +1086,16 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>80.2</v>
+      </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>❌ 無資料</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>🟢🟢 AI 需求爆(&gt;50%)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1023,6 +1109,14 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>1390</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,92 +449,72 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>價格</t>
+          <t>狀態</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>WTI</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>資料源</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>誤差</t>
-        </is>
-      </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>WTI</t>
+          <t>Cushing 庫存(千桶)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Cushing 庫存(千桶)</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>狀態</t>
+          <t>總 YoY%</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>核心 YoY%</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>總 YoY%</t>
+          <t>10Y%</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>核心 YoY%</t>
+          <t>月變動%</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>10Y%</t>
+          <t>10Y-2Y 利差%</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>月變動%</t>
+          <t>註</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>10Y-2Y 利差%</t>
+          <t>衰退機率%</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>註</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>衰退機率%</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
           <t>去年同期%</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>當季加總(億美)</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>計入家數</t>
         </is>
       </c>
     </row>
@@ -577,10 +557,6 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -592,22 +568,14 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>🟢 強(央行買盤)</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>4070.8</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>FMP=4070.8</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>❌ 無資料</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -619,10 +587,6 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -640,20 +604,20 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>84.38</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>FRED=84.38</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>84.38</v>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>411675</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -663,10 +627,6 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -684,17 +644,17 @@
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>FRED=0.6985, FMP=0.6984</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>FRED=0.6985</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0.6984</v>
-      </c>
+      <c r="K5" t="n">
+        <v>0.6985</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -703,10 +663,6 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -719,17 +675,17 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>❌ FRED+OECD 都失敗,手動查 https://web02.mof.gov.tw/njswww/WebMain.aspx</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>❌ FRED+OECD 都失敗,手動查 https://web02.mof.gov.tw/njswww/WebMain.aspx</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -737,10 +693,6 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -753,17 +705,17 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>❌ 無資料</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>❌ 無資料</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -771,10 +723,6 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -792,29 +740,25 @@
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>FRED=18.70, FMP=18.58</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FRED=18.70</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>18.7</v>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>18.64</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -841,22 +785,18 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
+      <c r="M9" t="n">
         <v>3.73</v>
       </c>
-      <c r="P9" t="n">
+      <c r="N9" t="n">
         <v>2.81</v>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -881,20 +821,16 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
+      <c r="O10" t="n">
         <v>4.71</v>
       </c>
-      <c r="R10" t="n">
+      <c r="P10" t="n">
         <v>0.21</v>
       </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -921,20 +857,16 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
+      <c r="Q11" t="n">
         <v>0.34</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Fed Futures 抓不到,用利差代理</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -947,17 +879,17 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>❌ MOVE 與 TLT 都抓不到</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>❌ MOVE 與 TLT 都抓不到</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -965,10 +897,6 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1001,14 +929,10 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1021,17 +945,17 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>❌ 無資料(FRED OECD series 變動)</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>❌ 無資料(FRED OECD series 變動)</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -1039,10 +963,6 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1055,17 +975,17 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>❌ 無資料(可改抓主計總處 stat.gov.tw)</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>❌ 無資料(可改抓主計總處 stat.gov.tw)</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -1073,10 +993,6 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1086,16 +1002,14 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
-        <v>80.2</v>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>🟢🟢 AI 需求爆(&gt;50%)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>❌ 無資料</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1109,14 +1023,6 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="n">
-        <v>1390</v>
-      </c>
-      <c r="X16" t="n">
-        <v>4</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -525,17 +525,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>330.9</v>
+        <v>331</v>
       </c>
       <c r="C2" t="n">
-        <v>328.1</v>
+        <v>327.4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>84.38</v>
+        <v>84.25</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=84.38</t>
+          <t>FRED=84.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>411675</t>
+          <t>404508</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.6985</t>
+          <t>FRED=0.6996</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.6985</v>
+        <v>0.6996</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=18.70</t>
+          <t>FRED=17.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>18.7</v>
+        <v>17.09</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -822,10 +822,10 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="P10" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -605,16 +605,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>84.25</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=84.25</t>
+          <t>FRED=81.96</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>404508</t>
+          <t>406987</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.6996</t>
+          <t>FRED=0.7026</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.6996</v>
+        <v>0.7026</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=17.09</t>
+          <t>FRED=15.15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>17.09</v>
+        <v>15.15</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -822,10 +822,10 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="P10" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -930,7 +930,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="T13" t="inlineStr"/>
     </row>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -605,16 +605,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>81.95999999999999</v>
+        <v>84.77</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=81.96</t>
+          <t>FRED=84.77</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>406987</t>
+          <t>424410</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.7026</t>
+          <t>FRED=0.7064</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.7026</v>
+        <v>0.7064</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=15.15</t>
+          <t>FRED=14.63</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>15.15</v>
+        <v>14.63</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -771,7 +771,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -786,10 +786,10 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>3.73</v>
+        <v>3.54</v>
       </c>
       <c r="N9" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -822,10 +822,10 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>4.69</v>
+        <v>4.63</v>
       </c>
       <c r="P10" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -605,16 +605,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>84.77</v>
+        <v>86.48</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=84.77</t>
+          <t>FRED=86.48</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>424410</t>
+          <t>428815</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.7064</t>
+          <t>FRED=0.7091</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.7064</v>
+        <v>0.7091</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=14.63</t>
+          <t>FRED=16.01</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>14.63</v>
+        <v>16.01</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -822,10 +822,10 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>4.63</v>
+        <v>4.69</v>
       </c>
       <c r="P10" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -525,17 +525,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>331</v>
+        <v>331.9</v>
       </c>
       <c r="C2" t="n">
-        <v>327.4</v>
+        <v>326.9</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1</v>
+        <v>1.52</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>86.48</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=86.48</t>
+          <t>FRED=83.90</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>428815</t>
+          <t>428910</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.7091</t>
+          <t>FRED=0.7178</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.7091</v>
+        <v>0.7178</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=16.01</t>
+          <t>FRED=14.51</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>16.01</v>
+        <v>14.51</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -822,11 +822,9 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.02</v>
-      </c>
+        <v>4.67</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -858,7 +856,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -600,21 +600,21 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>🟢 區間($60-85)</t>
+          <t>🔴 過熱(&gt;$90)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>83.90000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=83.90</t>
+          <t>FRED=91.48</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>428910</t>
+          <t>424460</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.7178</t>
+          <t>FRED=0.7166</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.7178</v>
+        <v>0.7166</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=14.51</t>
+          <t>FRED=14.32</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>14.51</v>
+        <v>14.32</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -822,9 +822,11 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
+        <v>4.77</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.14</v>
+      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -856,7 +858,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -907,7 +909,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -928,7 +930,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="T13" t="inlineStr"/>
     </row>
